--- a/order-form/Spread Sheets & Scripts/Country-Pricing-Master.xlsx
+++ b/order-form/Spread Sheets & Scripts/Country-Pricing-Master.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1300" uniqueCount="452">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1305" uniqueCount="453">
   <si>
     <t xml:space="preserve">country</t>
   </si>
@@ -443,6 +443,9 @@
   </si>
   <si>
     <t xml:space="preserve">https://egycgny.org/legalization/</t>
+  </si>
+  <si>
+    <t xml:space="preserve">El Salvador</t>
   </si>
   <si>
     <t xml:space="preserve">Hague Apostille Convention – the Convention entered into force for Ecuador on 2 April 2005, so documents normally require only an apostille rather than consular legalization.</t>
@@ -1679,7 +1682,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:L1048576"/>
+  <dimension ref="A1:L204"/>
   <sheetFormatPr defaultColWidth="10.16015625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="29.33"/>
@@ -3618,7 +3621,7 @@
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A53" s="1" t="s">
-        <v>135</v>
+        <v>141</v>
       </c>
       <c r="B53" s="1" t="s">
         <v>13</v>
@@ -3643,55 +3646,49 @@
       </c>
       <c r="I53" s="1" t="n">
         <v>0</v>
-      </c>
-      <c r="J53" s="4" t="n">
-        <v>38444</v>
-      </c>
-      <c r="K53" s="1" t="s">
-        <v>141</v>
-      </c>
-      <c r="L53" s="1" t="s">
-        <v>142</v>
       </c>
     </row>
     <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A54" s="1" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="B54" s="1" t="s">
         <v>13</v>
       </c>
       <c r="C54" s="1" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="D54" s="1" t="n">
-        <v>128</v>
+        <v>0</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>95</v>
+        <v>0</v>
       </c>
       <c r="F54" s="1" t="s">
         <v>20</v>
       </c>
       <c r="G54" s="1" t="s">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="H54" s="1" t="n">
-        <v>35</v>
+        <v>0</v>
       </c>
       <c r="I54" s="1" t="n">
         <v>0</v>
       </c>
+      <c r="J54" s="4" t="n">
+        <v>38444</v>
+      </c>
       <c r="K54" s="1" t="s">
+        <v>142</v>
+      </c>
+      <c r="L54" s="1" t="s">
         <v>143</v>
-      </c>
-      <c r="L54" s="1" t="s">
-        <v>144</v>
       </c>
     </row>
     <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A55" s="1" t="s">
-        <v>145</v>
+        <v>137</v>
       </c>
       <c r="B55" s="1" t="s">
         <v>13</v>
@@ -3700,7 +3697,7 @@
         <v>14</v>
       </c>
       <c r="D55" s="1" t="n">
-        <v>50</v>
+        <v>128</v>
       </c>
       <c r="E55" s="1" t="n">
         <v>95</v>
@@ -3709,261 +3706,258 @@
         <v>20</v>
       </c>
       <c r="G55" s="1" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="H55" s="1" t="n">
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="I55" s="1" t="n">
         <v>0</v>
       </c>
       <c r="K55" s="1" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="L55" s="1" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
     </row>
     <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A56" s="1" t="s">
+        <v>146</v>
+      </c>
+      <c r="B56" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C56" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="D56" s="1" t="n">
+        <v>50</v>
+      </c>
+      <c r="E56" s="1" t="n">
+        <v>95</v>
+      </c>
+      <c r="F56" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="G56" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="H56" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="I56" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="K56" s="1" t="s">
+        <v>147</v>
+      </c>
+      <c r="L56" s="1" t="s">
         <v>148</v>
-      </c>
-      <c r="B56" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="C56" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="D56" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="E56" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="F56" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="G56" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="H56" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="I56" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="J56" s="4" t="n">
-        <v>37164</v>
-      </c>
-      <c r="K56" s="1" t="s">
-        <v>149</v>
-      </c>
-      <c r="L56" s="1" t="s">
-        <v>150</v>
       </c>
     </row>
     <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A57" s="1" t="s">
+        <v>149</v>
+      </c>
+      <c r="B57" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C57" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D57" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="E57" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="F57" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="G57" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="H57" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="I57" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="J57" s="4" t="n">
+        <v>37164</v>
+      </c>
+      <c r="K57" s="1" t="s">
+        <v>150</v>
+      </c>
+      <c r="L57" s="1" t="s">
         <v>151</v>
-      </c>
-      <c r="B57" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="C57" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="D57" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="E57" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="F57" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="G57" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="H57" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="I57" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="J57" s="4" t="n">
-        <v>25087</v>
-      </c>
-      <c r="K57" s="1" t="s">
-        <v>152</v>
-      </c>
-      <c r="L57" s="1" t="s">
-        <v>153</v>
       </c>
     </row>
     <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A58" s="1" t="s">
+        <v>152</v>
+      </c>
+      <c r="B58" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C58" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D58" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="E58" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="F58" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="G58" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="H58" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="I58" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="J58" s="4" t="n">
+        <v>25087</v>
+      </c>
+      <c r="K58" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="L58" s="1" t="s">
         <v>154</v>
-      </c>
-      <c r="B58" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="C58" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="D58" s="1" t="n">
-        <v>95</v>
-      </c>
-      <c r="E58" s="1" t="n">
-        <v>95</v>
-      </c>
-      <c r="F58" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="G58" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="H58" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="I58" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="K58" s="1" t="s">
-        <v>155</v>
-      </c>
-      <c r="L58" s="1" t="s">
-        <v>156</v>
       </c>
     </row>
     <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A59" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="B59" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C59" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="D59" s="1" t="n">
+        <v>95</v>
+      </c>
+      <c r="E59" s="1" t="n">
+        <v>95</v>
+      </c>
+      <c r="F59" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="G59" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="H59" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="I59" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="K59" s="1" t="s">
+        <v>156</v>
+      </c>
+      <c r="L59" s="1" t="s">
         <v>157</v>
-      </c>
-      <c r="B59" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="C59" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="D59" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="E59" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="F59" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="G59" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="H59" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="I59" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="J59" s="4" t="n">
-        <v>26021</v>
-      </c>
-      <c r="K59" s="1" t="s">
-        <v>158</v>
-      </c>
-      <c r="L59" s="1" t="s">
-        <v>159</v>
       </c>
     </row>
     <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A60" s="1" t="s">
+        <v>158</v>
+      </c>
+      <c r="B60" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C60" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D60" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="E60" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="F60" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="G60" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="H60" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="I60" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="J60" s="4" t="n">
+        <v>26021</v>
+      </c>
+      <c r="K60" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="L60" s="1" t="s">
         <v>160</v>
-      </c>
-      <c r="B60" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="C60" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="D60" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="E60" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="F60" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="G60" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="H60" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="I60" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="J60" s="4" t="n">
-        <v>23893</v>
-      </c>
-      <c r="K60" s="1" t="s">
-        <v>161</v>
-      </c>
-      <c r="L60" s="1" t="s">
-        <v>162</v>
       </c>
     </row>
     <row r="61" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A61" s="1" t="s">
+        <v>161</v>
+      </c>
+      <c r="B61" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C61" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D61" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="E61" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="F61" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="G61" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="H61" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="I61" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="J61" s="4" t="n">
+        <v>23893</v>
+      </c>
+      <c r="K61" s="1" t="s">
+        <v>162</v>
+      </c>
+      <c r="L61" s="1" t="s">
         <v>163</v>
-      </c>
-      <c r="B61" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="C61" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="D61" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="E61" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="F61" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="G61" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="H61" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="I61" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="J61" s="4" t="n">
-        <v>23766</v>
-      </c>
-      <c r="K61" s="1" t="s">
-        <v>164</v>
-      </c>
-      <c r="L61" s="1" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="62" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A62" s="1" t="s">
-        <v>154</v>
+        <v>164</v>
       </c>
       <c r="B62" s="1" t="s">
         <v>13</v>
       </c>
       <c r="C62" s="1" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="D62" s="1" t="n">
-        <v>95</v>
+        <v>0</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>95</v>
+        <v>0</v>
       </c>
       <c r="F62" s="1" t="s">
         <v>20</v>
@@ -3977,463 +3971,466 @@
       <c r="I62" s="1" t="n">
         <v>0</v>
       </c>
+      <c r="J62" s="4" t="n">
+        <v>23766</v>
+      </c>
       <c r="K62" s="1" t="s">
-        <v>155</v>
+        <v>165</v>
       </c>
       <c r="L62" s="1" t="s">
-        <v>156</v>
+        <v>166</v>
       </c>
     </row>
     <row r="63" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A63" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="B63" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C63" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="D63" s="1" t="n">
+        <v>95</v>
+      </c>
+      <c r="E63" s="1" t="n">
+        <v>95</v>
+      </c>
+      <c r="F63" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="G63" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="H63" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="I63" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="K63" s="1" t="s">
+        <v>156</v>
+      </c>
+      <c r="L63" s="1" t="s">
         <v>157</v>
-      </c>
-      <c r="B63" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="C63" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="D63" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="E63" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="F63" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="G63" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="H63" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="I63" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="J63" s="4" t="n">
-        <v>26021</v>
-      </c>
-      <c r="K63" s="1" t="s">
-        <v>158</v>
-      </c>
-      <c r="L63" s="1" t="s">
-        <v>159</v>
       </c>
     </row>
     <row r="64" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A64" s="1" t="s">
+        <v>158</v>
+      </c>
+      <c r="B64" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C64" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D64" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="E64" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="F64" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="G64" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="H64" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="I64" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="J64" s="4" t="n">
+        <v>26021</v>
+      </c>
+      <c r="K64" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="L64" s="1" t="s">
         <v>160</v>
-      </c>
-      <c r="B64" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="C64" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="D64" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="E64" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="F64" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="G64" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="H64" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="I64" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="J64" s="4" t="n">
-        <v>23893</v>
-      </c>
-      <c r="K64" s="1" t="s">
-        <v>161</v>
-      </c>
-      <c r="L64" s="1" t="s">
-        <v>162</v>
       </c>
     </row>
     <row r="65" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A65" s="1" t="s">
+        <v>161</v>
+      </c>
+      <c r="B65" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C65" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D65" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="E65" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="F65" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="G65" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="H65" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="I65" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="J65" s="4" t="n">
+        <v>23893</v>
+      </c>
+      <c r="K65" s="1" t="s">
+        <v>162</v>
+      </c>
+      <c r="L65" s="1" t="s">
         <v>163</v>
-      </c>
-      <c r="B65" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="C65" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="D65" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="E65" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="F65" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="G65" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="H65" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="I65" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="J65" s="4" t="n">
-        <v>23766</v>
-      </c>
-      <c r="K65" s="1" t="s">
-        <v>164</v>
-      </c>
-      <c r="L65" s="1" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="66" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A66" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="B66" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C66" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D66" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="E66" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="F66" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="G66" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="H66" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="I66" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="J66" s="4" t="n">
+        <v>23766</v>
+      </c>
+      <c r="K66" s="1" t="s">
+        <v>165</v>
+      </c>
+      <c r="L66" s="1" t="s">
         <v>166</v>
-      </c>
-      <c r="B66" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="C66" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="D66" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="E66" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="F66" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="G66" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="H66" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="I66" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="J66" s="4" t="n">
-        <v>24117</v>
-      </c>
-      <c r="K66" s="1" t="s">
-        <v>167</v>
-      </c>
-      <c r="L66" s="1" t="s">
-        <v>168</v>
       </c>
     </row>
     <row r="67" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A67" s="1" t="s">
+        <v>167</v>
+      </c>
+      <c r="B67" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C67" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D67" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="E67" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="F67" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="G67" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="H67" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="I67" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="J67" s="4" t="n">
+        <v>24117</v>
+      </c>
+      <c r="K67" s="1" t="s">
+        <v>168</v>
+      </c>
+      <c r="L67" s="1" t="s">
         <v>169</v>
-      </c>
-      <c r="B67" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="C67" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="D67" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="E67" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="F67" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="G67" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="H67" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="I67" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="J67" s="4" t="n">
-        <v>35611</v>
-      </c>
-      <c r="K67" s="1" t="s">
-        <v>170</v>
-      </c>
-      <c r="L67" s="1" t="s">
-        <v>171</v>
       </c>
     </row>
     <row r="68" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A68" s="1" t="s">
+        <v>170</v>
+      </c>
+      <c r="B68" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C68" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D68" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="E68" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="F68" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="G68" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="H68" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="I68" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="J68" s="4" t="n">
+        <v>35611</v>
+      </c>
+      <c r="K68" s="1" t="s">
+        <v>171</v>
+      </c>
+      <c r="L68" s="1" t="s">
         <v>172</v>
-      </c>
-      <c r="B68" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="C68" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="D68" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="E68" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="F68" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="G68" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="H68" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="I68" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="J68" s="4" t="n">
-        <v>34833</v>
-      </c>
-      <c r="K68" s="1" t="s">
-        <v>173</v>
-      </c>
-      <c r="L68" s="1" t="s">
-        <v>174</v>
       </c>
     </row>
     <row r="69" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A69" s="1" t="s">
+        <v>173</v>
+      </c>
+      <c r="B69" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C69" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D69" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="E69" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="F69" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="G69" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="H69" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="I69" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="J69" s="4" t="n">
+        <v>34833</v>
+      </c>
+      <c r="K69" s="1" t="s">
+        <v>174</v>
+      </c>
+      <c r="L69" s="1" t="s">
         <v>175</v>
-      </c>
-      <c r="B69" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="C69" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="D69" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="E69" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="F69" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="G69" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="H69" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="I69" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="J69" s="4" t="n">
-        <v>24151</v>
-      </c>
-      <c r="K69" s="1" t="s">
-        <v>176</v>
-      </c>
-      <c r="L69" s="1" t="s">
-        <v>177</v>
       </c>
     </row>
     <row r="70" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A70" s="1" t="s">
+        <v>176</v>
+      </c>
+      <c r="B70" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C70" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D70" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="E70" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="F70" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="G70" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="H70" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="I70" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="J70" s="4" t="n">
+        <v>24151</v>
+      </c>
+      <c r="K70" s="1" t="s">
+        <v>177</v>
+      </c>
+      <c r="L70" s="1" t="s">
         <v>178</v>
-      </c>
-      <c r="B70" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="C70" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="D70" s="1" t="n">
-        <v>30</v>
-      </c>
-      <c r="E70" s="1" t="n">
-        <v>95</v>
-      </c>
-      <c r="F70" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="G70" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="H70" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="I70" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="K70" s="1" t="s">
-        <v>179</v>
-      </c>
-      <c r="L70" s="1" t="s">
-        <v>180</v>
       </c>
     </row>
     <row r="71" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A71" s="1" t="s">
+        <v>179</v>
+      </c>
+      <c r="B71" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C71" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="D71" s="1" t="n">
+        <v>30</v>
+      </c>
+      <c r="E71" s="1" t="n">
+        <v>95</v>
+      </c>
+      <c r="F71" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="G71" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="H71" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="I71" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="K71" s="1" t="s">
+        <v>180</v>
+      </c>
+      <c r="L71" s="1" t="s">
         <v>181</v>
-      </c>
-      <c r="B71" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="C71" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="D71" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="E71" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="F71" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="G71" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="H71" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="I71" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="K71" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="L71" s="1" t="s">
-        <v>182</v>
       </c>
     </row>
     <row r="72" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A72" s="1" t="s">
+        <v>182</v>
+      </c>
+      <c r="B72" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C72" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D72" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="E72" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="F72" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="G72" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="H72" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="I72" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="K72" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="L72" s="1" t="s">
         <v>183</v>
-      </c>
-      <c r="B72" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="C72" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="D72" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="E72" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="F72" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="G72" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="H72" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="I72" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="J72" s="4" t="n">
-        <v>37353</v>
-      </c>
-      <c r="K72" s="1" t="s">
-        <v>184</v>
-      </c>
-      <c r="L72" s="1" t="s">
-        <v>185</v>
       </c>
     </row>
     <row r="73" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A73" s="1" t="s">
+        <v>184</v>
+      </c>
+      <c r="B73" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C73" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D73" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="E73" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="F73" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="G73" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="H73" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="I73" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="J73" s="4" t="n">
+        <v>37353</v>
+      </c>
+      <c r="K73" s="1" t="s">
+        <v>185</v>
+      </c>
+      <c r="L73" s="1" t="s">
         <v>186</v>
-      </c>
-      <c r="B73" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="C73" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="D73" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="E73" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="F73" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="G73" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="H73" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="I73" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="J73" s="4" t="n">
-        <v>42996</v>
-      </c>
-      <c r="K73" s="1" t="s">
-        <v>187</v>
-      </c>
-      <c r="L73" s="1" t="s">
-        <v>188</v>
       </c>
     </row>
     <row r="74" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A74" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="B74" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C74" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D74" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="E74" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="F74" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="G74" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="H74" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="I74" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="J74" s="4" t="n">
+        <v>42996</v>
+      </c>
+      <c r="K74" s="1" t="s">
+        <v>188</v>
+      </c>
+      <c r="L74" s="1" t="s">
         <v>189</v>
-      </c>
-      <c r="B74" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="C74" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="D74" s="1" t="n">
-        <v>200</v>
-      </c>
-      <c r="E74" s="1" t="n">
-        <v>95</v>
-      </c>
-      <c r="F74" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="G74" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="H74" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="I74" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="K74" s="1" t="s">
-        <v>190</v>
-      </c>
-      <c r="L74" s="1" t="s">
-        <v>191</v>
       </c>
     </row>
     <row r="75" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A75" s="1" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="B75" s="1" t="s">
         <v>13</v>
@@ -4442,7 +4439,7 @@
         <v>14</v>
       </c>
       <c r="D75" s="1" t="n">
-        <v>105</v>
+        <v>200</v>
       </c>
       <c r="E75" s="1" t="n">
         <v>95</v>
@@ -4460,121 +4457,118 @@
         <v>0</v>
       </c>
       <c r="K75" s="1" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="L75" s="1" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
     </row>
     <row r="76" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A76" s="1" t="s">
+        <v>193</v>
+      </c>
+      <c r="B76" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C76" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="D76" s="1" t="n">
+        <v>105</v>
+      </c>
+      <c r="E76" s="1" t="n">
+        <v>95</v>
+      </c>
+      <c r="F76" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="G76" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="H76" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="I76" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="K76" s="1" t="s">
+        <v>194</v>
+      </c>
+      <c r="L76" s="1" t="s">
         <v>195</v>
-      </c>
-      <c r="B76" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="C76" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="D76" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="E76" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="F76" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="G76" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="H76" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="I76" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="J76" s="4" t="n">
-        <v>43573</v>
-      </c>
-      <c r="K76" s="1" t="s">
-        <v>196</v>
-      </c>
-      <c r="L76" s="1" t="s">
-        <v>197</v>
       </c>
     </row>
     <row r="77" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A77" s="1" t="s">
+        <v>196</v>
+      </c>
+      <c r="B77" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C77" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D77" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="E77" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="F77" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="G77" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="H77" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="I77" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="J77" s="4" t="n">
+        <v>43573</v>
+      </c>
+      <c r="K77" s="1" t="s">
+        <v>197</v>
+      </c>
+      <c r="L77" s="1" t="s">
         <v>198</v>
-      </c>
-      <c r="B77" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="C77" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="D77" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="E77" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="F77" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="G77" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="H77" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="I77" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="J77" s="4" t="n">
-        <v>45304</v>
-      </c>
-      <c r="K77" s="1" t="s">
-        <v>199</v>
-      </c>
-      <c r="L77" s="1" t="s">
-        <v>29</v>
       </c>
     </row>
     <row r="78" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A78" s="1" t="s">
+        <v>199</v>
+      </c>
+      <c r="B78" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C78" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D78" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="E78" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="F78" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="G78" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="H78" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="I78" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="J78" s="4" t="n">
+        <v>45304</v>
+      </c>
+      <c r="K78" s="1" t="s">
         <v>200</v>
-      </c>
-      <c r="B78" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="C78" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="D78" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="E78" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="F78" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="G78" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="H78" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="I78" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="J78" s="4" t="n">
-        <v>38006</v>
-      </c>
-      <c r="K78" s="1" t="s">
-        <v>201</v>
       </c>
       <c r="L78" s="1" t="s">
         <v>29</v>
@@ -4582,223 +4576,229 @@
     </row>
     <row r="79" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A79" s="1" t="s">
+        <v>201</v>
+      </c>
+      <c r="B79" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C79" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D79" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="E79" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="F79" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="G79" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="H79" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="I79" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="J79" s="4" t="n">
+        <v>38006</v>
+      </c>
+      <c r="K79" s="1" t="s">
         <v>202</v>
       </c>
-      <c r="B79" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="C79" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="D79" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="E79" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="F79" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="G79" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="H79" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="I79" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="J79" s="4" t="n">
-        <v>23857</v>
-      </c>
-      <c r="K79" s="1" t="s">
-        <v>203</v>
+      <c r="L79" s="1" t="s">
+        <v>29</v>
       </c>
     </row>
     <row r="80" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A80" s="1" t="s">
+        <v>203</v>
+      </c>
+      <c r="B80" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C80" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D80" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="E80" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="F80" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="G80" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="H80" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="I80" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="J80" s="4" t="n">
+        <v>23857</v>
+      </c>
+      <c r="K80" s="1" t="s">
         <v>204</v>
-      </c>
-      <c r="B80" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="C80" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="D80" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="E80" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="F80" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="G80" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="H80" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="I80" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="J80" s="4" t="n">
-        <v>26682</v>
-      </c>
-      <c r="K80" s="1" t="s">
-        <v>205</v>
       </c>
     </row>
     <row r="81" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A81" s="1" t="s">
+        <v>205</v>
+      </c>
+      <c r="B81" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C81" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D81" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="E81" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="F81" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="G81" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="H81" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="I81" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="J81" s="4" t="n">
+        <v>26682</v>
+      </c>
+      <c r="K81" s="1" t="s">
         <v>206</v>
-      </c>
-      <c r="B81" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="C81" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="D81" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="E81" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="F81" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="G81" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="H81" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="I81" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="J81" s="4" t="n">
-        <v>38318</v>
-      </c>
-      <c r="K81" s="1" t="s">
-        <v>207</v>
       </c>
     </row>
     <row r="82" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A82" s="1" t="s">
+        <v>207</v>
+      </c>
+      <c r="B82" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C82" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D82" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="E82" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="F82" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="G82" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="H82" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="I82" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="J82" s="4" t="n">
+        <v>38318</v>
+      </c>
+      <c r="K82" s="1" t="s">
         <v>208</v>
-      </c>
-      <c r="B82" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="C82" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="D82" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="E82" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="F82" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="G82" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="H82" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="I82" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="J82" s="4" t="n">
-        <v>38547</v>
-      </c>
-      <c r="K82" s="1" t="s">
-        <v>209</v>
       </c>
     </row>
     <row r="83" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A83" s="1" t="s">
+        <v>209</v>
+      </c>
+      <c r="B83" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C83" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D83" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="E83" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="F83" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="G83" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="H83" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="I83" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="J83" s="4" t="n">
+        <v>38547</v>
+      </c>
+      <c r="K83" s="1" t="s">
         <v>210</v>
-      </c>
-      <c r="B83" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="C83" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="D83" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="E83" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="F83" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="G83" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="H83" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="I83" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="J83" s="4" t="n">
-        <v>44716</v>
-      </c>
-      <c r="K83" s="1" t="s">
-        <v>211</v>
       </c>
     </row>
     <row r="84" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A84" s="1" t="s">
+        <v>211</v>
+      </c>
+      <c r="B84" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C84" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D84" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="E84" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="F84" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="G84" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="H84" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="I84" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="J84" s="4" t="n">
+        <v>44716</v>
+      </c>
+      <c r="K84" s="1" t="s">
         <v>212</v>
-      </c>
-      <c r="B84" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="C84" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="D84" s="1" t="n">
-        <v>100</v>
-      </c>
-      <c r="E84" s="1" t="n">
-        <v>95</v>
-      </c>
-      <c r="F84" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="G84" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="H84" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="I84" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="K84" s="1" t="s">
-        <v>213</v>
       </c>
     </row>
     <row r="85" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A85" s="1" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="B85" s="1" t="s">
-        <v>215</v>
+        <v>13</v>
       </c>
       <c r="C85" s="1" t="s">
         <v>14</v>
       </c>
       <c r="D85" s="1" t="n">
-        <v>15</v>
+        <v>100</v>
       </c>
       <c r="E85" s="1" t="n">
         <v>95</v>
@@ -4816,21 +4816,21 @@
         <v>0</v>
       </c>
       <c r="K85" s="1" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
     </row>
     <row r="86" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A86" s="1" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="B86" s="1" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="C86" s="1" t="s">
         <v>14</v>
       </c>
       <c r="D86" s="1" t="n">
-        <v>160</v>
+        <v>15</v>
       </c>
       <c r="E86" s="1" t="n">
         <v>95</v>
@@ -4848,228 +4848,228 @@
         <v>0</v>
       </c>
       <c r="K86" s="1" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
     </row>
     <row r="87" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A87" s="1" t="s">
+        <v>218</v>
+      </c>
+      <c r="B87" s="1" t="s">
+        <v>219</v>
+      </c>
+      <c r="C87" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="D87" s="1" t="n">
+        <v>160</v>
+      </c>
+      <c r="E87" s="1" t="n">
+        <v>95</v>
+      </c>
+      <c r="F87" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="G87" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="H87" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="I87" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="K87" s="1" t="s">
         <v>220</v>
-      </c>
-      <c r="B87" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="C87" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="D87" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="E87" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="F87" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="G87" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="H87" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="I87" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="J87" s="4" t="n">
-        <v>36228</v>
-      </c>
-      <c r="K87" s="1" t="s">
-        <v>221</v>
       </c>
     </row>
     <row r="88" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A88" s="1" t="s">
+        <v>221</v>
+      </c>
+      <c r="B88" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C88" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D88" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="E88" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="F88" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="G88" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="H88" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="I88" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="J88" s="4" t="n">
+        <v>36228</v>
+      </c>
+      <c r="K88" s="1" t="s">
         <v>222</v>
-      </c>
-      <c r="B88" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="C88" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="D88" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="E88" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="F88" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="G88" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="H88" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="I88" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="J88" s="4" t="n">
-        <v>28716</v>
-      </c>
-      <c r="K88" s="1" t="s">
-        <v>223</v>
       </c>
     </row>
     <row r="89" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A89" s="1" t="s">
+        <v>223</v>
+      </c>
+      <c r="B89" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C89" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D89" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="E89" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="F89" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="G89" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="H89" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="I89" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="J89" s="4" t="n">
+        <v>28716</v>
+      </c>
+      <c r="K89" s="1" t="s">
         <v>224</v>
-      </c>
-      <c r="B89" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="C89" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="D89" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="E89" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="F89" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="G89" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="H89" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="I89" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="J89" s="4" t="n">
-        <v>28532</v>
-      </c>
-      <c r="K89" s="1" t="s">
-        <v>225</v>
       </c>
     </row>
     <row r="90" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A90" s="1" t="s">
+        <v>225</v>
+      </c>
+      <c r="B90" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C90" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D90" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="E90" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="F90" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="G90" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="H90" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="I90" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="J90" s="4" t="n">
+        <v>28532</v>
+      </c>
+      <c r="K90" s="1" t="s">
         <v>226</v>
-      </c>
-      <c r="B90" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="C90" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="D90" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="E90" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="F90" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="G90" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="H90" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="I90" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="J90" s="4" t="n">
-        <v>44380</v>
-      </c>
-      <c r="K90" s="1" t="s">
-        <v>227</v>
       </c>
     </row>
     <row r="91" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A91" s="1" t="s">
+        <v>227</v>
+      </c>
+      <c r="B91" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C91" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D91" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="E91" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="F91" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="G91" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="H91" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="I91" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="J91" s="4" t="n">
+        <v>44380</v>
+      </c>
+      <c r="K91" s="1" t="s">
         <v>228</v>
-      </c>
-      <c r="B91" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="C91" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="D91" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="E91" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="F91" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="G91" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="H91" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="I91" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="J91" s="4" t="n">
-        <v>25776</v>
-      </c>
-      <c r="K91" s="1" t="s">
-        <v>229</v>
       </c>
     </row>
     <row r="92" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A92" s="1" t="s">
+        <v>229</v>
+      </c>
+      <c r="B92" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C92" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D92" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="E92" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="F92" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="G92" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="H92" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="I92" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="J92" s="4" t="n">
+        <v>25776</v>
+      </c>
+      <c r="K92" s="1" t="s">
         <v>230</v>
-      </c>
-      <c r="B92" s="1" t="s">
-        <v>215</v>
-      </c>
-      <c r="C92" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="D92" s="1" t="n">
-        <v>15</v>
-      </c>
-      <c r="E92" s="1" t="n">
-        <v>95</v>
-      </c>
-      <c r="F92" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="G92" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="H92" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="I92" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="K92" s="1" t="s">
-        <v>231</v>
       </c>
     </row>
     <row r="93" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A93" s="1" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="B93" s="1" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="C93" s="1" t="s">
         <v>14</v>
       </c>
       <c r="D93" s="1" t="n">
-        <v>50</v>
+        <v>15</v>
       </c>
       <c r="E93" s="1" t="n">
         <v>95</v>
@@ -5087,79 +5087,79 @@
         <v>0</v>
       </c>
       <c r="K93" s="1" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
     </row>
     <row r="94" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A94" s="1" t="s">
+        <v>233</v>
+      </c>
+      <c r="B94" s="1" t="s">
+        <v>219</v>
+      </c>
+      <c r="C94" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="D94" s="1" t="n">
+        <v>50</v>
+      </c>
+      <c r="E94" s="1" t="n">
+        <v>95</v>
+      </c>
+      <c r="F94" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="G94" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="H94" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="I94" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="K94" s="1" t="s">
         <v>234</v>
-      </c>
-      <c r="B94" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="C94" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="D94" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="E94" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="F94" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="G94" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="H94" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="I94" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="J94" s="4" t="n">
-        <v>36921</v>
-      </c>
-      <c r="K94" s="1" t="s">
-        <v>235</v>
       </c>
     </row>
     <row r="95" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A95" s="1" t="s">
+        <v>235</v>
+      </c>
+      <c r="B95" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C95" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D95" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="E95" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="F95" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="G95" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="H95" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="I95" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="J95" s="4" t="n">
+        <v>36921</v>
+      </c>
+      <c r="K95" s="1" t="s">
         <v>236</v>
-      </c>
-      <c r="B95" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="C95" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="D95" s="1" t="n">
-        <v>50</v>
-      </c>
-      <c r="E95" s="1" t="n">
-        <v>95</v>
-      </c>
-      <c r="F95" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="G95" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="H95" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="I95" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="K95" s="1" t="s">
-        <v>237</v>
       </c>
     </row>
     <row r="96" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A96" s="1" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="B96" s="1" t="s">
         <v>13</v>
@@ -5174,7 +5174,7 @@
         <v>95</v>
       </c>
       <c r="F96" s="1" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="G96" s="1" t="s">
         <v>15</v>
@@ -5186,27 +5186,27 @@
         <v>0</v>
       </c>
       <c r="K96" s="1" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
     </row>
     <row r="97" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A97" s="1" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="B97" s="1" t="s">
-        <v>215</v>
+        <v>13</v>
       </c>
       <c r="C97" s="1" t="s">
         <v>14</v>
       </c>
       <c r="D97" s="1" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="E97" s="1" t="n">
         <v>95</v>
       </c>
       <c r="F97" s="1" t="s">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="G97" s="1" t="s">
         <v>15</v>
@@ -5218,21 +5218,21 @@
         <v>0</v>
       </c>
       <c r="K97" s="1" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
     </row>
     <row r="98" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A98" s="1" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="B98" s="1" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="C98" s="1" t="s">
         <v>14</v>
       </c>
       <c r="D98" s="1" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="E98" s="1" t="n">
         <v>95</v>
@@ -5250,15 +5250,15 @@
         <v>0</v>
       </c>
       <c r="K98" s="1" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
     </row>
     <row r="99" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A99" s="1" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="B99" s="1" t="s">
-        <v>13</v>
+        <v>219</v>
       </c>
       <c r="C99" s="1" t="s">
         <v>14</v>
@@ -5282,88 +5282,88 @@
         <v>0</v>
       </c>
       <c r="K99" s="1" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
     </row>
     <row r="100" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A100" s="1" t="s">
+        <v>245</v>
+      </c>
+      <c r="B100" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C100" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="D100" s="1" t="n">
+        <v>50</v>
+      </c>
+      <c r="E100" s="1" t="n">
+        <v>95</v>
+      </c>
+      <c r="F100" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="G100" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="H100" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="I100" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="K100" s="1" t="s">
         <v>246</v>
-      </c>
-      <c r="B100" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="C100" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="D100" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="E100" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="F100" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="G100" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="H100" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="I100" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="J100" s="4" t="n">
-        <v>35094</v>
-      </c>
-      <c r="K100" s="1" t="s">
-        <v>247</v>
       </c>
     </row>
     <row r="101" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A101" s="1" t="s">
+        <v>247</v>
+      </c>
+      <c r="B101" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C101" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D101" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="E101" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="F101" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="G101" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="H101" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="I101" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="J101" s="4" t="n">
+        <v>35094</v>
+      </c>
+      <c r="K101" s="1" t="s">
         <v>248</v>
-      </c>
-      <c r="B101" s="1" t="s">
-        <v>215</v>
-      </c>
-      <c r="C101" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="D101" s="1" t="n">
-        <v>40</v>
-      </c>
-      <c r="E101" s="1" t="n">
-        <v>95</v>
-      </c>
-      <c r="F101" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="G101" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="H101" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="I101" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="K101" s="1" t="s">
-        <v>249</v>
       </c>
     </row>
     <row r="102" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A102" s="1" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="B102" s="1" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="C102" s="1" t="s">
         <v>14</v>
       </c>
       <c r="D102" s="1" t="n">
-        <v>90</v>
+        <v>40</v>
       </c>
       <c r="E102" s="1" t="n">
         <v>95</v>
@@ -5381,117 +5381,117 @@
         <v>0</v>
       </c>
       <c r="K102" s="1" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
     </row>
     <row r="103" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A103" s="1" t="s">
+        <v>251</v>
+      </c>
+      <c r="B103" s="1" t="s">
+        <v>219</v>
+      </c>
+      <c r="C103" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="D103" s="1" t="n">
+        <v>90</v>
+      </c>
+      <c r="E103" s="1" t="n">
+        <v>95</v>
+      </c>
+      <c r="F103" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="G103" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="H103" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="I103" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="K103" s="1" t="s">
         <v>252</v>
-      </c>
-      <c r="B103" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="C103" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="D103" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="E103" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="F103" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="G103" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="H103" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="I103" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="J103" s="4" t="n">
-        <v>25776</v>
-      </c>
-      <c r="K103" s="1" t="s">
-        <v>253</v>
       </c>
     </row>
     <row r="104" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A104" s="1" t="s">
+        <v>253</v>
+      </c>
+      <c r="B104" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C104" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D104" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="E104" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="F104" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="G104" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="H104" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="I104" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="J104" s="4" t="n">
+        <v>25776</v>
+      </c>
+      <c r="K104" s="1" t="s">
         <v>254</v>
-      </c>
-      <c r="B104" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="C104" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="D104" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="E104" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="F104" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="G104" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="H104" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="I104" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="J104" s="4" t="n">
-        <v>35103</v>
-      </c>
-      <c r="K104" s="1" t="s">
-        <v>255</v>
       </c>
     </row>
     <row r="105" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A105" s="1" t="s">
+        <v>255</v>
+      </c>
+      <c r="B105" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C105" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D105" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="E105" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="F105" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="G105" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="H105" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="I105" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="J105" s="4" t="n">
+        <v>35103</v>
+      </c>
+      <c r="K105" s="1" t="s">
         <v>256</v>
-      </c>
-      <c r="B105" s="1" t="s">
-        <v>215</v>
-      </c>
-      <c r="C105" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="D105" s="1" t="n">
-        <v>100</v>
-      </c>
-      <c r="E105" s="1" t="n">
-        <v>95</v>
-      </c>
-      <c r="F105" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="G105" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="H105" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="I105" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="K105" s="1" t="s">
-        <v>257</v>
       </c>
     </row>
     <row r="106" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A106" s="1" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="B106" s="1" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="C106" s="1" t="s">
         <v>14</v>
@@ -5515,216 +5515,216 @@
         <v>0</v>
       </c>
       <c r="K106" s="1" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
     </row>
     <row r="107" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A107" s="1" t="s">
+        <v>259</v>
+      </c>
+      <c r="B107" s="1" t="s">
+        <v>219</v>
+      </c>
+      <c r="C107" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="D107" s="1" t="n">
+        <v>100</v>
+      </c>
+      <c r="E107" s="1" t="n">
+        <v>95</v>
+      </c>
+      <c r="F107" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="G107" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="H107" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="I107" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="K107" s="1" t="s">
         <v>260</v>
-      </c>
-      <c r="B107" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="C107" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="D107" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="E107" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="F107" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="G107" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="H107" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="I107" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="J107" s="4" t="n">
-        <v>26541</v>
-      </c>
-      <c r="K107" s="1" t="s">
-        <v>261</v>
       </c>
     </row>
     <row r="108" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A108" s="1" t="s">
+        <v>261</v>
+      </c>
+      <c r="B108" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C108" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D108" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="E108" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="F108" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="G108" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="H108" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="I108" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="J108" s="4" t="n">
+        <v>26541</v>
+      </c>
+      <c r="K108" s="1" t="s">
         <v>262</v>
-      </c>
-      <c r="B108" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="C108" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="D108" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="E108" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="F108" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="G108" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="H108" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="I108" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="J108" s="4" t="n">
-        <v>35630</v>
-      </c>
-      <c r="K108" s="1" t="s">
-        <v>263</v>
       </c>
     </row>
     <row r="109" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A109" s="1" t="s">
+        <v>263</v>
+      </c>
+      <c r="B109" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C109" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D109" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="E109" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="F109" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="G109" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="H109" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="I109" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="J109" s="4" t="n">
+        <v>35630</v>
+      </c>
+      <c r="K109" s="1" t="s">
         <v>264</v>
-      </c>
-      <c r="B109" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="C109" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="D109" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="E109" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="F109" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="G109" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="H109" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="I109" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="J109" s="4" t="n">
-        <v>29009</v>
-      </c>
-      <c r="K109" s="1" t="s">
-        <v>265</v>
       </c>
     </row>
     <row r="110" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A110" s="1" t="s">
+        <v>265</v>
+      </c>
+      <c r="B110" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C110" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D110" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="E110" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="F110" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="G110" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="H110" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="I110" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="J110" s="4" t="n">
+        <v>29009</v>
+      </c>
+      <c r="K110" s="1" t="s">
         <v>266</v>
-      </c>
-      <c r="B110" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="C110" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="D110" s="1" t="n">
-        <v>10</v>
-      </c>
-      <c r="E110" s="1" t="n">
-        <v>95</v>
-      </c>
-      <c r="F110" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="G110" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="H110" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="I110" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="K110" s="1" t="s">
-        <v>267</v>
       </c>
     </row>
     <row r="111" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A111" s="1" t="s">
+        <v>267</v>
+      </c>
+      <c r="B111" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C111" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="D111" s="1" t="n">
+        <v>10</v>
+      </c>
+      <c r="E111" s="1" t="n">
+        <v>95</v>
+      </c>
+      <c r="F111" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="G111" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="H111" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="I111" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="K111" s="1" t="s">
         <v>268</v>
-      </c>
-      <c r="B111" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="C111" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="D111" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="E111" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="F111" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="G111" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="H111" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="I111" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="J111" s="4" t="n">
-        <v>24808</v>
-      </c>
-      <c r="K111" s="1" t="s">
-        <v>269</v>
       </c>
     </row>
     <row r="112" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A112" s="1" t="s">
+        <v>269</v>
+      </c>
+      <c r="B112" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C112" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D112" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="E112" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="F112" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="G112" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="H112" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="I112" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="J112" s="4" t="n">
+        <v>24808</v>
+      </c>
+      <c r="K112" s="1" t="s">
         <v>270</v>
-      </c>
-      <c r="B112" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="C112" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="D112" s="1" t="n">
-        <v>5</v>
-      </c>
-      <c r="E112" s="1" t="n">
-        <v>95</v>
-      </c>
-      <c r="F112" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="G112" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="H112" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="I112" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="K112" s="1" t="s">
-        <v>271</v>
       </c>
     </row>
     <row r="113" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A113" s="1" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="B113" s="1" t="s">
         <v>13</v>
@@ -5733,7 +5733,7 @@
         <v>14</v>
       </c>
       <c r="D113" s="1" t="n">
-        <v>50</v>
+        <v>5</v>
       </c>
       <c r="E113" s="1" t="n">
         <v>95</v>
@@ -5751,12 +5751,12 @@
         <v>0</v>
       </c>
       <c r="K113" s="1" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
     </row>
     <row r="114" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A114" s="1" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="B114" s="1" t="s">
         <v>13</v>
@@ -5765,7 +5765,7 @@
         <v>14</v>
       </c>
       <c r="D114" s="1" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="E114" s="1" t="n">
         <v>95</v>
@@ -5783,426 +5783,426 @@
         <v>0</v>
       </c>
       <c r="K114" s="1" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
     </row>
     <row r="115" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A115" s="1" t="s">
+        <v>275</v>
+      </c>
+      <c r="B115" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C115" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="D115" s="1" t="n">
+        <v>10</v>
+      </c>
+      <c r="E115" s="1" t="n">
+        <v>95</v>
+      </c>
+      <c r="F115" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="G115" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="H115" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="I115" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="K115" s="1" t="s">
         <v>276</v>
-      </c>
-      <c r="B115" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="C115" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="D115" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="E115" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="F115" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="G115" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="H115" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="I115" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="J115" s="4" t="n">
-        <v>24927</v>
-      </c>
-      <c r="K115" s="1" t="s">
-        <v>277</v>
       </c>
     </row>
     <row r="116" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A116" s="1" t="s">
+        <v>277</v>
+      </c>
+      <c r="B116" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C116" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D116" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="E116" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="F116" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="G116" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="H116" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="I116" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="J116" s="4" t="n">
+        <v>24927</v>
+      </c>
+      <c r="K116" s="1" t="s">
         <v>278</v>
-      </c>
-      <c r="B116" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="C116" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="D116" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="E116" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="F116" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="G116" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="H116" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="I116" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="J116" s="4" t="n">
-        <v>33830</v>
-      </c>
-      <c r="K116" s="1" t="s">
-        <v>279</v>
       </c>
     </row>
     <row r="117" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A117" s="1" t="s">
+        <v>279</v>
+      </c>
+      <c r="B117" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C117" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D117" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="E117" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="F117" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="G117" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="H117" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="I117" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="J117" s="4" t="n">
+        <v>33830</v>
+      </c>
+      <c r="K117" s="1" t="s">
         <v>280</v>
-      </c>
-      <c r="B117" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="C117" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="D117" s="1" t="n">
-        <v>30</v>
-      </c>
-      <c r="E117" s="1" t="n">
-        <v>95</v>
-      </c>
-      <c r="F117" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="G117" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="H117" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="I117" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="K117" s="1" t="s">
-        <v>281</v>
       </c>
     </row>
     <row r="118" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A118" s="1" t="s">
+        <v>281</v>
+      </c>
+      <c r="B118" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C118" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="D118" s="1" t="n">
+        <v>30</v>
+      </c>
+      <c r="E118" s="1" t="n">
+        <v>95</v>
+      </c>
+      <c r="F118" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="G118" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="H118" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="I118" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="K118" s="1" t="s">
         <v>282</v>
-      </c>
-      <c r="B118" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="C118" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="D118" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="E118" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="F118" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="G118" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="H118" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="I118" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="J118" s="4" t="n">
-        <v>24909</v>
-      </c>
-      <c r="K118" s="1" t="s">
-        <v>283</v>
       </c>
     </row>
     <row r="119" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A119" s="1" t="s">
+        <v>283</v>
+      </c>
+      <c r="B119" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C119" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D119" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="E119" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="F119" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="G119" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="H119" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="I119" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="J119" s="4" t="n">
+        <v>24909</v>
+      </c>
+      <c r="K119" s="1" t="s">
         <v>284</v>
-      </c>
-      <c r="B119" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="C119" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="D119" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="E119" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="F119" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="G119" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="H119" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="I119" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="J119" s="4" t="n">
-        <v>34925</v>
-      </c>
-      <c r="K119" s="1" t="s">
-        <v>285</v>
       </c>
     </row>
     <row r="120" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A120" s="1" t="s">
+        <v>285</v>
+      </c>
+      <c r="B120" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C120" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D120" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="E120" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="F120" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="G120" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="H120" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="I120" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="J120" s="4" t="n">
+        <v>34925</v>
+      </c>
+      <c r="K120" s="1" t="s">
         <v>286</v>
-      </c>
-      <c r="B120" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="C120" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="D120" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="E120" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="F120" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="G120" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="H120" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="I120" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="J120" s="4" t="n">
-        <v>36402</v>
-      </c>
-      <c r="K120" s="1" t="s">
-        <v>287</v>
       </c>
     </row>
     <row r="121" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A121" s="1" t="s">
+        <v>287</v>
+      </c>
+      <c r="B121" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C121" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D121" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="E121" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="F121" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="G121" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="H121" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="I121" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="J121" s="4" t="n">
+        <v>36402</v>
+      </c>
+      <c r="K121" s="1" t="s">
         <v>288</v>
-      </c>
-      <c r="B121" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="C121" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="D121" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="E121" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="F121" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="G121" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="H121" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="I121" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="J121" s="4" t="n">
-        <v>39157</v>
-      </c>
-      <c r="K121" s="1" t="s">
-        <v>289</v>
       </c>
     </row>
     <row r="122" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A122" s="1" t="s">
+        <v>289</v>
+      </c>
+      <c r="B122" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C122" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D122" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="E122" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="F122" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="G122" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="H122" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="I122" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="J122" s="4" t="n">
+        <v>39157</v>
+      </c>
+      <c r="K122" s="1" t="s">
         <v>290</v>
-      </c>
-      <c r="B122" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="C122" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="D122" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="E122" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="F122" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="G122" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="H122" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="I122" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="J122" s="4" t="n">
-        <v>37622</v>
-      </c>
-      <c r="K122" s="1" t="s">
-        <v>291</v>
       </c>
     </row>
     <row r="123" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A123" s="1" t="s">
+        <v>291</v>
+      </c>
+      <c r="B123" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C123" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D123" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="E123" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="F123" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="G123" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="H123" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="I123" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="J123" s="4" t="n">
+        <v>37622</v>
+      </c>
+      <c r="K123" s="1" t="s">
         <v>292</v>
-      </c>
-      <c r="B123" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="C123" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="D123" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="E123" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="F123" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="G123" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="H123" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="I123" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="J123" s="4" t="n">
-        <v>40122</v>
-      </c>
-      <c r="K123" s="1" t="s">
-        <v>293</v>
       </c>
     </row>
     <row r="124" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A124" s="1" t="s">
+        <v>293</v>
+      </c>
+      <c r="B124" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C124" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D124" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="E124" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="F124" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="G124" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="H124" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="I124" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="J124" s="4" t="n">
+        <v>40122</v>
+      </c>
+      <c r="K124" s="1" t="s">
         <v>294</v>
-      </c>
-      <c r="B124" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="C124" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="D124" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="E124" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="F124" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="G124" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="H124" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="I124" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="J124" s="4" t="n">
-        <v>38901</v>
-      </c>
-      <c r="K124" s="1" t="s">
-        <v>295</v>
       </c>
     </row>
     <row r="125" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A125" s="1" t="s">
+        <v>295</v>
+      </c>
+      <c r="B125" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C125" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D125" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="E125" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="F125" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="G125" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="H125" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="I125" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="J125" s="4" t="n">
+        <v>38901</v>
+      </c>
+      <c r="K125" s="1" t="s">
         <v>296</v>
-      </c>
-      <c r="B125" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="C125" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="D125" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="E125" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="F125" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="G125" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="H125" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="I125" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="J125" s="4" t="n">
-        <v>42596</v>
-      </c>
-      <c r="K125" s="1" t="s">
-        <v>297</v>
       </c>
     </row>
     <row r="126" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A126" s="1" t="s">
+        <v>297</v>
+      </c>
+      <c r="B126" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C126" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D126" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="E126" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="F126" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="G126" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="H126" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="I126" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="J126" s="4" t="n">
+        <v>42596</v>
+      </c>
+      <c r="K126" s="1" t="s">
         <v>298</v>
-      </c>
-      <c r="B126" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="C126" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="D126" s="1" t="n">
-        <v>50</v>
-      </c>
-      <c r="E126" s="1" t="n">
-        <v>95</v>
-      </c>
-      <c r="F126" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="G126" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="H126" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="I126" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="K126" s="1" t="s">
-        <v>299</v>
       </c>
     </row>
     <row r="127" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A127" s="1" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="B127" s="1" t="s">
         <v>13</v>
@@ -6211,7 +6211,7 @@
         <v>14</v>
       </c>
       <c r="D127" s="1" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="E127" s="1" t="n">
         <v>95</v>
@@ -6229,251 +6229,251 @@
         <v>0</v>
       </c>
       <c r="K127" s="1" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
     </row>
     <row r="128" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A128" s="1" t="s">
+        <v>301</v>
+      </c>
+      <c r="B128" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C128" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="D128" s="1" t="n">
+        <v>60</v>
+      </c>
+      <c r="E128" s="1" t="n">
+        <v>95</v>
+      </c>
+      <c r="F128" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="G128" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="H128" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="I128" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="K128" s="1" t="s">
         <v>302</v>
-      </c>
-      <c r="B128" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="C128" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="D128" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="E128" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="F128" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="G128" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="H128" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="I128" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="J128" s="4" t="n">
-        <v>36921</v>
-      </c>
-      <c r="K128" s="1" t="s">
-        <v>303</v>
       </c>
     </row>
     <row r="129" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A129" s="1" t="s">
+        <v>303</v>
+      </c>
+      <c r="B129" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C129" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D129" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="E129" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="F129" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="G129" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="H129" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="I129" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="J129" s="4" t="n">
+        <v>36921</v>
+      </c>
+      <c r="K129" s="1" t="s">
         <v>304</v>
-      </c>
-      <c r="B129" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="C129" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="D129" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="E129" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="F129" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="G129" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="H129" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="I129" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="J129" s="4" t="n">
-        <v>42246</v>
-      </c>
-      <c r="K129" s="1" t="s">
-        <v>305</v>
       </c>
     </row>
     <row r="130" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A130" s="1" t="s">
+        <v>305</v>
+      </c>
+      <c r="B130" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C130" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D130" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="E130" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="F130" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="G130" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="H130" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="I130" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="J130" s="4" t="n">
+        <v>42246</v>
+      </c>
+      <c r="K130" s="1" t="s">
         <v>306</v>
-      </c>
-      <c r="B130" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="C130" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="D130" s="1" t="n">
-        <v>35</v>
-      </c>
-      <c r="E130" s="1" t="n">
-        <v>95</v>
-      </c>
-      <c r="F130" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="G130" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="H130" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="I130" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="K130" s="1" t="s">
-        <v>307</v>
       </c>
     </row>
     <row r="131" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A131" s="1" t="s">
+        <v>307</v>
+      </c>
+      <c r="B131" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C131" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="D131" s="1" t="n">
+        <v>35</v>
+      </c>
+      <c r="E131" s="1" t="n">
+        <v>95</v>
+      </c>
+      <c r="F131" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="G131" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="H131" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="I131" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="K131" s="1" t="s">
         <v>308</v>
-      </c>
-      <c r="B131" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="C131" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="D131" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="E131" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="F131" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="G131" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="H131" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="I131" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="J131" s="4" t="n">
-        <v>23766</v>
-      </c>
-      <c r="K131" s="1" t="s">
-        <v>309</v>
       </c>
     </row>
     <row r="132" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A132" s="1" t="s">
+        <v>309</v>
+      </c>
+      <c r="B132" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C132" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D132" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="E132" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="F132" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="G132" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="H132" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="I132" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="J132" s="4" t="n">
+        <v>23766</v>
+      </c>
+      <c r="K132" s="1" t="s">
         <v>310</v>
-      </c>
-      <c r="B132" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="C132" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="D132" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="E132" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="F132" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="G132" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="H132" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="I132" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="J132" s="4" t="n">
-        <v>37217</v>
-      </c>
-      <c r="K132" s="1" t="s">
-        <v>311</v>
       </c>
     </row>
     <row r="133" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A133" s="1" t="s">
+        <v>311</v>
+      </c>
+      <c r="B133" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C133" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D133" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="E133" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="F133" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="G133" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="H133" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="I133" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="J133" s="4" t="n">
+        <v>37217</v>
+      </c>
+      <c r="K133" s="1" t="s">
         <v>312</v>
-      </c>
-      <c r="B133" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="C133" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="D133" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="E133" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="F133" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="G133" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="H133" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="I133" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="J133" s="4" t="n">
-        <v>41408</v>
-      </c>
-      <c r="K133" s="1" t="s">
-        <v>313</v>
       </c>
     </row>
     <row r="134" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A134" s="1" t="s">
+        <v>313</v>
+      </c>
+      <c r="B134" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C134" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D134" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="E134" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="F134" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="G134" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="H134" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="I134" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="J134" s="4" t="n">
+        <v>41408</v>
+      </c>
+      <c r="K134" s="1" t="s">
         <v>314</v>
-      </c>
-      <c r="B134" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="C134" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="D134" s="1" t="n">
-        <v>65</v>
-      </c>
-      <c r="E134" s="1" t="n">
-        <v>95</v>
-      </c>
-      <c r="F134" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="G134" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="H134" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="I134" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="K134" s="1" t="s">
-        <v>315</v>
       </c>
     </row>
     <row r="135" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A135" s="1" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="B135" s="1" t="s">
         <v>13</v>
@@ -6482,7 +6482,7 @@
         <v>14</v>
       </c>
       <c r="D135" s="1" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="E135" s="1" t="n">
         <v>95</v>
@@ -6500,181 +6500,181 @@
         <v>0</v>
       </c>
       <c r="K135" s="1" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
     </row>
     <row r="136" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A136" s="1" t="s">
+        <v>317</v>
+      </c>
+      <c r="B136" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C136" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="D136" s="1" t="n">
+        <v>100</v>
+      </c>
+      <c r="E136" s="1" t="n">
+        <v>95</v>
+      </c>
+      <c r="F136" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="G136" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="H136" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="I136" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="K136" s="1" t="s">
         <v>318</v>
-      </c>
-      <c r="B136" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="C136" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="D136" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="E136" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="F136" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="G136" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="H136" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="I136" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="J136" s="4" t="n">
-        <v>36221</v>
-      </c>
-      <c r="K136" s="1" t="s">
-        <v>319</v>
       </c>
     </row>
     <row r="137" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A137" s="1" t="s">
+        <v>319</v>
+      </c>
+      <c r="B137" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C137" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D137" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="E137" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="F137" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="G137" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="H137" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="I137" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="J137" s="4" t="n">
+        <v>36221</v>
+      </c>
+      <c r="K137" s="1" t="s">
         <v>320</v>
-      </c>
-      <c r="B137" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="C137" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="D137" s="1" t="n">
-        <v>50</v>
-      </c>
-      <c r="E137" s="1" t="n">
-        <v>95</v>
-      </c>
-      <c r="F137" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="G137" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="H137" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="I137" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="K137" s="1" t="s">
-        <v>321</v>
       </c>
     </row>
     <row r="138" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A138" s="1" t="s">
+        <v>321</v>
+      </c>
+      <c r="B138" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C138" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="D138" s="1" t="n">
+        <v>50</v>
+      </c>
+      <c r="E138" s="1" t="n">
+        <v>95</v>
+      </c>
+      <c r="F138" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="G138" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="H138" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="I138" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="K138" s="1" t="s">
         <v>322</v>
-      </c>
-      <c r="B138" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="C138" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="D138" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="E138" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="F138" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="G138" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="H138" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="I138" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="J138" s="4" t="n">
-        <v>33559</v>
-      </c>
-      <c r="K138" s="1" t="s">
-        <v>323</v>
       </c>
     </row>
     <row r="139" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A139" s="1" t="s">
+        <v>323</v>
+      </c>
+      <c r="B139" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C139" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D139" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="E139" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="F139" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="G139" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="H139" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="I139" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="J139" s="4" t="n">
+        <v>33559</v>
+      </c>
+      <c r="K139" s="1" t="s">
         <v>324</v>
-      </c>
-      <c r="B139" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="C139" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="D139" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="E139" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="F139" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="G139" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="H139" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="I139" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="J139" s="4" t="n">
-        <v>30529</v>
-      </c>
-      <c r="K139" s="1" t="s">
-        <v>325</v>
       </c>
     </row>
     <row r="140" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A140" s="1" t="s">
+        <v>325</v>
+      </c>
+      <c r="B140" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C140" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D140" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="E140" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="F140" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="G140" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="H140" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="I140" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="J140" s="4" t="n">
+        <v>30529</v>
+      </c>
+      <c r="K140" s="1" t="s">
         <v>326</v>
-      </c>
-      <c r="B140" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="C140" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="D140" s="1" t="n">
-        <v>150</v>
-      </c>
-      <c r="E140" s="1" t="n">
-        <v>95</v>
-      </c>
-      <c r="F140" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="G140" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="H140" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="I140" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="K140" s="1" t="s">
-        <v>327</v>
       </c>
     </row>
     <row r="141" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A141" s="1" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="B141" s="1" t="s">
         <v>13</v>
@@ -6683,7 +6683,7 @@
         <v>14</v>
       </c>
       <c r="D141" s="1" t="n">
-        <v>30</v>
+        <v>150</v>
       </c>
       <c r="E141" s="1" t="n">
         <v>95</v>
@@ -6701,972 +6701,972 @@
         <v>0</v>
       </c>
       <c r="K141" s="1" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
     </row>
     <row r="142" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A142" s="1" t="s">
+        <v>329</v>
+      </c>
+      <c r="B142" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C142" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="D142" s="1" t="n">
+        <v>30</v>
+      </c>
+      <c r="E142" s="1" t="n">
+        <v>95</v>
+      </c>
+      <c r="F142" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="G142" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="H142" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="I142" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="K142" s="1" t="s">
         <v>330</v>
-      </c>
-      <c r="B142" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="C142" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="D142" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="E142" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="F142" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="G142" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="H142" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="I142" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="J142" s="4" t="n">
-        <v>44005</v>
-      </c>
-      <c r="K142" s="1" t="s">
-        <v>331</v>
       </c>
     </row>
     <row r="143" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A143" s="1" t="s">
+        <v>331</v>
+      </c>
+      <c r="B143" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C143" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D143" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="E143" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="F143" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="G143" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="H143" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="I143" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="J143" s="4" t="n">
+        <v>44005</v>
+      </c>
+      <c r="K143" s="1" t="s">
         <v>332</v>
-      </c>
-      <c r="B143" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="C143" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="D143" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="E143" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="F143" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="G143" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="H143" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="I143" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="J143" s="4" t="n">
-        <v>41408</v>
-      </c>
-      <c r="K143" s="1" t="s">
-        <v>333</v>
       </c>
     </row>
     <row r="144" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A144" s="1" t="s">
+        <v>333</v>
+      </c>
+      <c r="B144" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C144" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D144" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="E144" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="F144" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="G144" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="H144" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="I144" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="J144" s="4" t="n">
+        <v>41408</v>
+      </c>
+      <c r="K144" s="1" t="s">
         <v>334</v>
-      </c>
-      <c r="B144" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="C144" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="D144" s="1" t="n">
-        <v>50</v>
-      </c>
-      <c r="E144" s="1" t="n">
-        <v>95</v>
-      </c>
-      <c r="F144" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="G144" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="H144" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="I144" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="K144" s="1" t="s">
-        <v>335</v>
       </c>
     </row>
     <row r="145" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A145" s="1" t="s">
+        <v>335</v>
+      </c>
+      <c r="B145" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C145" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="D145" s="1" t="n">
+        <v>50</v>
+      </c>
+      <c r="E145" s="1" t="n">
+        <v>95</v>
+      </c>
+      <c r="F145" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="G145" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="H145" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="I145" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="K145" s="1" t="s">
         <v>336</v>
-      </c>
-      <c r="B145" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="C145" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="D145" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="E145" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="F145" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="G145" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="H145" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="I145" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="J145" s="4" t="n">
-        <v>41881</v>
-      </c>
-      <c r="K145" s="1" t="s">
-        <v>337</v>
       </c>
     </row>
     <row r="146" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A146" s="1" t="s">
+        <v>337</v>
+      </c>
+      <c r="B146" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C146" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D146" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="E146" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="F146" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="G146" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="H146" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="I146" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="J146" s="4" t="n">
+        <v>41881</v>
+      </c>
+      <c r="K146" s="1" t="s">
         <v>338</v>
-      </c>
-      <c r="B146" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="C146" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="D146" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="E146" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="F146" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="G146" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="H146" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="I146" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="J146" s="4" t="n">
-        <v>40451</v>
-      </c>
-      <c r="K146" s="1" t="s">
-        <v>339</v>
       </c>
     </row>
     <row r="147" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A147" s="1" t="s">
+        <v>339</v>
+      </c>
+      <c r="B147" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C147" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D147" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="E147" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="F147" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="G147" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="H147" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="I147" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="J147" s="4" t="n">
+        <v>40451</v>
+      </c>
+      <c r="K147" s="1" t="s">
         <v>340</v>
-      </c>
-      <c r="B147" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="C147" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="D147" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="E147" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="F147" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="G147" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="H147" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="I147" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="J147" s="4" t="n">
-        <v>43599</v>
-      </c>
-      <c r="K147" s="1" t="s">
-        <v>341</v>
       </c>
     </row>
     <row r="148" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A148" s="1" t="s">
+        <v>341</v>
+      </c>
+      <c r="B148" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C148" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D148" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="E148" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="F148" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="G148" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="H148" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="I148" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="J148" s="4" t="n">
+        <v>43599</v>
+      </c>
+      <c r="K148" s="1" t="s">
         <v>342</v>
-      </c>
-      <c r="B148" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="C148" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="D148" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="E148" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="F148" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="G148" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="H148" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="I148" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="J148" s="4" t="n">
-        <v>38578</v>
-      </c>
-      <c r="K148" s="1" t="s">
-        <v>343</v>
       </c>
     </row>
     <row r="149" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A149" s="1" t="s">
+        <v>343</v>
+      </c>
+      <c r="B149" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C149" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D149" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="E149" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="F149" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="G149" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="H149" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="I149" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="J149" s="4" t="n">
+        <v>38578</v>
+      </c>
+      <c r="K149" s="1" t="s">
         <v>344</v>
-      </c>
-      <c r="B149" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="C149" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="D149" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="E149" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="F149" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="G149" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="H149" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="I149" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="J149" s="4" t="n">
-        <v>25238</v>
-      </c>
-      <c r="K149" s="1" t="s">
-        <v>345</v>
       </c>
     </row>
     <row r="150" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A150" s="1" t="s">
+        <v>345</v>
+      </c>
+      <c r="B150" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C150" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D150" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="E150" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="F150" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="G150" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="H150" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="I150" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="J150" s="4" t="n">
+        <v>25238</v>
+      </c>
+      <c r="K150" s="1" t="s">
         <v>346</v>
-      </c>
-      <c r="B150" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="C150" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="D150" s="1" t="n">
-        <v>40</v>
-      </c>
-      <c r="E150" s="1" t="n">
-        <v>95</v>
-      </c>
-      <c r="F150" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="G150" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="H150" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="I150" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="K150" s="1" t="s">
-        <v>347</v>
       </c>
     </row>
     <row r="151" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A151" s="1" t="s">
+        <v>347</v>
+      </c>
+      <c r="B151" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C151" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="D151" s="1" t="n">
+        <v>40</v>
+      </c>
+      <c r="E151" s="1" t="n">
+        <v>95</v>
+      </c>
+      <c r="F151" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="G151" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="H151" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="I151" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="K151" s="1" t="s">
         <v>348</v>
-      </c>
-      <c r="B151" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="C151" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="D151" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="E151" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="F151" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="G151" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="H151" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="I151" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="J151" s="4" t="n">
-        <v>36966</v>
-      </c>
-      <c r="K151" s="1" t="s">
-        <v>349</v>
       </c>
     </row>
     <row r="152" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A152" s="1" t="s">
+        <v>349</v>
+      </c>
+      <c r="B152" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C152" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D152" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="E152" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="F152" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="G152" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="H152" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="I152" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="J152" s="4" t="n">
+        <v>36966</v>
+      </c>
+      <c r="K152" s="1" t="s">
         <v>350</v>
-      </c>
-      <c r="B152" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="C152" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="D152" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="E152" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="F152" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="G152" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="H152" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="I152" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="J152" s="4" t="n">
-        <v>33755</v>
-      </c>
-      <c r="K152" s="1" t="s">
-        <v>351</v>
       </c>
     </row>
     <row r="153" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A153" s="1" t="s">
+        <v>351</v>
+      </c>
+      <c r="B153" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C153" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D153" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="E153" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="F153" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="G153" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="H153" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="I153" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="J153" s="4" t="n">
+        <v>33755</v>
+      </c>
+      <c r="K153" s="1" t="s">
         <v>352</v>
-      </c>
-      <c r="B153" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="C153" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="D153" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="E153" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="F153" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="G153" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="H153" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="I153" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="J153" s="4" t="n">
-        <v>45448</v>
-      </c>
-      <c r="K153" s="1" t="s">
-        <v>353</v>
       </c>
     </row>
     <row r="154" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A154" s="1" t="s">
+        <v>353</v>
+      </c>
+      <c r="B154" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C154" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D154" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="E154" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="F154" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="G154" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="H154" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="I154" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="J154" s="4" t="n">
+        <v>45448</v>
+      </c>
+      <c r="K154" s="1" t="s">
         <v>354</v>
-      </c>
-      <c r="B154" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="C154" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="D154" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="E154" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="F154" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="G154" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="H154" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="I154" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="J154" s="4" t="n">
-        <v>37622</v>
-      </c>
-      <c r="K154" s="1" t="s">
-        <v>355</v>
       </c>
     </row>
     <row r="155" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A155" s="1" t="s">
+        <v>355</v>
+      </c>
+      <c r="B155" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C155" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D155" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="E155" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="F155" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="G155" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="H155" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="I155" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="J155" s="4" t="n">
+        <v>37622</v>
+      </c>
+      <c r="K155" s="1" t="s">
         <v>356</v>
-      </c>
-      <c r="B155" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="C155" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="D155" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="E155" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="F155" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="G155" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="H155" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="I155" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="J155" s="4" t="n">
-        <v>37468</v>
-      </c>
-      <c r="K155" s="1" t="s">
-        <v>357</v>
       </c>
     </row>
     <row r="156" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A156" s="1" t="s">
+        <v>357</v>
+      </c>
+      <c r="B156" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C156" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D156" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="E156" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="F156" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="G156" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="H156" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="I156" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="J156" s="4" t="n">
+        <v>37468</v>
+      </c>
+      <c r="K156" s="1" t="s">
         <v>358</v>
-      </c>
-      <c r="B156" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="C156" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="D156" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="E156" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="F156" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="G156" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="H156" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="I156" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="J156" s="4" t="n">
-        <v>37622</v>
-      </c>
-      <c r="K156" s="1" t="s">
-        <v>359</v>
       </c>
     </row>
     <row r="157" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A157" s="1" t="s">
+        <v>359</v>
+      </c>
+      <c r="B157" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C157" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D157" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="E157" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="F157" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="G157" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="H157" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="I157" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="J157" s="4" t="n">
+        <v>37622</v>
+      </c>
+      <c r="K157" s="1" t="s">
         <v>360</v>
-      </c>
-      <c r="B157" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="C157" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="D157" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="E157" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="F157" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="G157" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="H157" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="I157" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="J157" s="4" t="n">
-        <v>36416</v>
-      </c>
-      <c r="K157" s="1" t="s">
-        <v>361</v>
       </c>
     </row>
     <row r="158" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A158" s="1" t="s">
+        <v>361</v>
+      </c>
+      <c r="B158" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C158" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D158" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="E158" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="F158" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="G158" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="H158" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="I158" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="J158" s="4" t="n">
+        <v>36416</v>
+      </c>
+      <c r="K158" s="1" t="s">
         <v>362</v>
-      </c>
-      <c r="B158" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="C158" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="D158" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="E158" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="F158" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="G158" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="H158" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="I158" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="J158" s="4" t="n">
-        <v>34743</v>
-      </c>
-      <c r="K158" s="1" t="s">
-        <v>363</v>
       </c>
     </row>
     <row r="159" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A159" s="1" t="s">
+        <v>363</v>
+      </c>
+      <c r="B159" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C159" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D159" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="E159" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="F159" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="G159" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="H159" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="I159" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="J159" s="4" t="n">
+        <v>34743</v>
+      </c>
+      <c r="K159" s="1" t="s">
         <v>364</v>
-      </c>
-      <c r="B159" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="C159" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="D159" s="1" t="n">
-        <v>10</v>
-      </c>
-      <c r="E159" s="1" t="n">
-        <v>95</v>
-      </c>
-      <c r="F159" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="G159" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="H159" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="I159" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="K159" s="1" t="s">
-        <v>365</v>
       </c>
     </row>
     <row r="160" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A160" s="1" t="s">
+        <v>365</v>
+      </c>
+      <c r="B160" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C160" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="D160" s="1" t="n">
+        <v>10</v>
+      </c>
+      <c r="E160" s="1" t="n">
+        <v>95</v>
+      </c>
+      <c r="F160" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="G160" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="H160" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="I160" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="K160" s="1" t="s">
         <v>366</v>
-      </c>
-      <c r="B160" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="C160" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="D160" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="E160" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="F160" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="G160" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="H160" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="I160" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="J160" s="4" t="n">
-        <v>45008</v>
-      </c>
-      <c r="K160" s="1" t="s">
-        <v>367</v>
       </c>
     </row>
     <row r="161" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A161" s="1" t="s">
+        <v>367</v>
+      </c>
+      <c r="B161" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C161" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D161" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="E161" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="F161" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="G161" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="H161" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="I161" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="J161" s="4" t="n">
+        <v>45008</v>
+      </c>
+      <c r="K161" s="1" t="s">
         <v>368</v>
-      </c>
-      <c r="B161" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="C161" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="D161" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="E161" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="F161" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="G161" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="H161" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="I161" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="J161" s="4" t="n">
-        <v>33721</v>
-      </c>
-      <c r="K161" s="1" t="s">
-        <v>369</v>
       </c>
     </row>
     <row r="162" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A162" s="1" t="s">
+        <v>369</v>
+      </c>
+      <c r="B162" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C162" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D162" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="E162" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="F162" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="G162" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="H162" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="I162" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="J162" s="4" t="n">
+        <v>33721</v>
+      </c>
+      <c r="K162" s="1" t="s">
         <v>370</v>
-      </c>
-      <c r="B162" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="C162" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="D162" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="E162" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="F162" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="G162" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="H162" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="I162" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="J162" s="4" t="n">
-        <v>28945</v>
-      </c>
-      <c r="K162" s="1" t="s">
-        <v>371</v>
       </c>
     </row>
     <row r="163" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A163" s="1" t="s">
+        <v>371</v>
+      </c>
+      <c r="B163" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C163" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D163" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="E163" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="F163" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="G163" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="H163" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="I163" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="J163" s="4" t="n">
+        <v>28945</v>
+      </c>
+      <c r="K163" s="1" t="s">
         <v>372</v>
-      </c>
-      <c r="B163" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="C163" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="D163" s="1" t="n">
-        <v>60</v>
-      </c>
-      <c r="E163" s="1" t="n">
-        <v>95</v>
-      </c>
-      <c r="F163" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="G163" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="H163" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="I163" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="K163" s="1" t="s">
-        <v>373</v>
       </c>
     </row>
     <row r="164" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A164" s="1" t="s">
+        <v>373</v>
+      </c>
+      <c r="B164" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C164" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="D164" s="1" t="n">
+        <v>60</v>
+      </c>
+      <c r="E164" s="1" t="n">
+        <v>95</v>
+      </c>
+      <c r="F164" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="G164" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="H164" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="I164" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="K164" s="1" t="s">
         <v>374</v>
-      </c>
-      <c r="B164" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="C164" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="D164" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="E164" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="F164" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="G164" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="H164" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="I164" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="J164" s="4" t="n">
-        <v>44455</v>
-      </c>
-      <c r="K164" s="1" t="s">
-        <v>375</v>
       </c>
     </row>
     <row r="165" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A165" s="1" t="s">
+        <v>375</v>
+      </c>
+      <c r="B165" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C165" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D165" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="E165" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="F165" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="G165" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="H165" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="I165" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="J165" s="4" t="n">
+        <v>44455</v>
+      </c>
+      <c r="K165" s="1" t="s">
         <v>376</v>
-      </c>
-      <c r="B165" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="C165" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="D165" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="E165" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="F165" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="G165" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="H165" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="I165" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="J165" s="4" t="n">
-        <v>37305</v>
-      </c>
-      <c r="K165" s="1" t="s">
-        <v>377</v>
       </c>
     </row>
     <row r="166" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A166" s="1" t="s">
+        <v>377</v>
+      </c>
+      <c r="B166" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C166" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D166" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="E166" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="F166" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="G166" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="H166" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="I166" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="J166" s="4" t="n">
+        <v>37305</v>
+      </c>
+      <c r="K166" s="1" t="s">
         <v>378</v>
-      </c>
-      <c r="B166" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="C166" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="D166" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="E166" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="F166" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="G166" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="H166" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="I166" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="J166" s="4" t="n">
-        <v>33763</v>
-      </c>
-      <c r="K166" s="1" t="s">
-        <v>379</v>
       </c>
     </row>
     <row r="167" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A167" s="1" t="s">
+        <v>379</v>
+      </c>
+      <c r="B167" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C167" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D167" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="E167" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="F167" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="G167" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="H167" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="I167" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="J167" s="4" t="n">
+        <v>33763</v>
+      </c>
+      <c r="K167" s="1" t="s">
         <v>380</v>
-      </c>
-      <c r="B167" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="C167" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="D167" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="E167" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="F167" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="G167" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="H167" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="I167" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="J167" s="4" t="n">
-        <v>34171</v>
-      </c>
-      <c r="K167" s="1" t="s">
-        <v>381</v>
       </c>
     </row>
     <row r="168" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A168" s="1" t="s">
+        <v>381</v>
+      </c>
+      <c r="B168" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C168" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D168" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="E168" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="F168" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="G168" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="H168" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="I168" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="J168" s="4" t="n">
+        <v>34171</v>
+      </c>
+      <c r="K168" s="1" t="s">
         <v>382</v>
-      </c>
-      <c r="B168" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="C168" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="D168" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="E168" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="F168" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="G168" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="H168" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="I168" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="J168" s="4" t="n">
-        <v>45381</v>
-      </c>
-      <c r="K168" s="1" t="s">
-        <v>383</v>
       </c>
     </row>
     <row r="169" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A169" s="1" t="s">
+        <v>383</v>
+      </c>
+      <c r="B169" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C169" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D169" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="E169" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="F169" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="G169" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="H169" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="I169" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="J169" s="4" t="n">
+        <v>45381</v>
+      </c>
+      <c r="K169" s="1" t="s">
         <v>384</v>
-      </c>
-      <c r="B169" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="C169" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="D169" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="E169" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="F169" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="G169" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="H169" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="I169" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="K169" s="1" t="s">
-        <v>21</v>
       </c>
     </row>
     <row r="170" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7709,13 +7709,13 @@
         <v>13</v>
       </c>
       <c r="C171" s="1" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="D171" s="1" t="n">
         <v>0</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>95</v>
+        <v>0</v>
       </c>
       <c r="F171" s="1" t="s">
         <v>20</v>
@@ -7730,39 +7730,39 @@
         <v>0</v>
       </c>
       <c r="K171" s="1" t="s">
-        <v>387</v>
+        <v>21</v>
       </c>
     </row>
     <row r="172" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A172" s="1" t="s">
+        <v>387</v>
+      </c>
+      <c r="B172" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C172" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="D172" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="E172" s="1" t="n">
+        <v>95</v>
+      </c>
+      <c r="F172" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="G172" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="H172" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="I172" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="K172" s="1" t="s">
         <v>388</v>
-      </c>
-      <c r="B172" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="C172" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="D172" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="E172" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="F172" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="G172" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="H172" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="I172" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="K172" s="1" t="s">
-        <v>21</v>
       </c>
     </row>
     <row r="173" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7773,13 +7773,13 @@
         <v>13</v>
       </c>
       <c r="C173" s="1" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="D173" s="1" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>95</v>
+        <v>0</v>
       </c>
       <c r="F173" s="1" t="s">
         <v>20</v>
@@ -7794,12 +7794,12 @@
         <v>0</v>
       </c>
       <c r="K173" s="1" t="s">
-        <v>390</v>
+        <v>21</v>
       </c>
     </row>
     <row r="174" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A174" s="1" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="B174" s="1" t="s">
         <v>13</v>
@@ -7826,283 +7826,283 @@
         <v>0</v>
       </c>
       <c r="K174" s="1" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
     </row>
     <row r="175" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A175" s="1" t="s">
+        <v>392</v>
+      </c>
+      <c r="B175" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C175" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="D175" s="1" t="n">
+        <v>60</v>
+      </c>
+      <c r="E175" s="1" t="n">
+        <v>95</v>
+      </c>
+      <c r="F175" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="G175" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="H175" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="I175" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="K175" s="1" t="s">
         <v>393</v>
-      </c>
-      <c r="B175" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="C175" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="D175" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="E175" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="F175" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="G175" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="H175" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="I175" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="J175" s="4" t="n">
-        <v>28058</v>
-      </c>
-      <c r="K175" s="1" t="s">
-        <v>394</v>
       </c>
     </row>
     <row r="176" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A176" s="1" t="s">
+        <v>394</v>
+      </c>
+      <c r="B176" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C176" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D176" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="E176" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="F176" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="G176" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="H176" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="I176" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="J176" s="4" t="n">
+        <v>28058</v>
+      </c>
+      <c r="K176" s="1" t="s">
         <v>395</v>
-      </c>
-      <c r="B176" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="C176" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="D176" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="E176" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="F176" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="G176" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="H176" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="I176" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="J176" s="4" t="n">
-        <v>36281</v>
-      </c>
-      <c r="K176" s="1" t="s">
-        <v>396</v>
       </c>
     </row>
     <row r="177" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A177" s="1" t="s">
+        <v>396</v>
+      </c>
+      <c r="B177" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C177" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D177" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="E177" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="F177" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="G177" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="H177" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="I177" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="J177" s="4" t="n">
+        <v>36281</v>
+      </c>
+      <c r="K177" s="1" t="s">
         <v>397</v>
-      </c>
-      <c r="B177" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="C177" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="D177" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="E177" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="F177" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="G177" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="H177" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="I177" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="J177" s="4" t="n">
-        <v>26734</v>
-      </c>
-      <c r="K177" s="1" t="s">
-        <v>398</v>
       </c>
     </row>
     <row r="178" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A178" s="1" t="s">
+        <v>398</v>
+      </c>
+      <c r="B178" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C178" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D178" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="E178" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="F178" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="G178" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="H178" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="I178" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="J178" s="4" t="n">
+        <v>26734</v>
+      </c>
+      <c r="K178" s="1" t="s">
         <v>399</v>
-      </c>
-      <c r="B178" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="C178" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="D178" s="1" t="n">
-        <v>80</v>
-      </c>
-      <c r="E178" s="1" t="n">
-        <v>95</v>
-      </c>
-      <c r="F178" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="G178" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="H178" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="I178" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="K178" s="1" t="s">
-        <v>400</v>
       </c>
     </row>
     <row r="179" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A179" s="1" t="s">
+        <v>400</v>
+      </c>
+      <c r="B179" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C179" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="D179" s="1" t="n">
+        <v>80</v>
+      </c>
+      <c r="E179" s="1" t="n">
+        <v>95</v>
+      </c>
+      <c r="F179" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="G179" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="H179" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="I179" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="K179" s="1" t="s">
         <v>401</v>
-      </c>
-      <c r="B179" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="C179" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="D179" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="E179" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="F179" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="G179" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="H179" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="I179" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="J179" s="4" t="n">
-        <v>41468</v>
-      </c>
-      <c r="K179" s="1" t="s">
-        <v>402</v>
       </c>
     </row>
     <row r="180" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A180" s="1" t="s">
+        <v>402</v>
+      </c>
+      <c r="B180" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C180" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D180" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="E180" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="F180" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="G180" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="H180" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="I180" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="J180" s="4" t="n">
+        <v>41468</v>
+      </c>
+      <c r="K180" s="1" t="s">
         <v>403</v>
-      </c>
-      <c r="B180" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="C180" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="D180" s="1" t="n">
-        <v>50</v>
-      </c>
-      <c r="E180" s="1" t="n">
-        <v>95</v>
-      </c>
-      <c r="F180" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="G180" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="H180" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="I180" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="K180" s="1" t="s">
-        <v>404</v>
       </c>
     </row>
     <row r="181" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A181" s="1" t="s">
+        <v>404</v>
+      </c>
+      <c r="B181" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C181" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="D181" s="1" t="n">
+        <v>50</v>
+      </c>
+      <c r="E181" s="1" t="n">
+        <v>95</v>
+      </c>
+      <c r="F181" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="G181" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="H181" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="I181" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="K181" s="1" t="s">
         <v>405</v>
-      </c>
-      <c r="B181" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="C181" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="D181" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="E181" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="F181" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="G181" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="H181" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="I181" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="J181" s="4" t="n">
-        <v>42308</v>
-      </c>
-      <c r="K181" s="1" t="s">
-        <v>406</v>
       </c>
     </row>
     <row r="182" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A182" s="1" t="s">
+        <v>406</v>
+      </c>
+      <c r="B182" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C182" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D182" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="E182" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="F182" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="G182" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="H182" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="I182" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="J182" s="4" t="n">
+        <v>42308</v>
+      </c>
+      <c r="K182" s="1" t="s">
         <v>407</v>
-      </c>
-      <c r="B182" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="C182" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="D182" s="1" t="n">
-        <v>60</v>
-      </c>
-      <c r="E182" s="1" t="n">
-        <v>95</v>
-      </c>
-      <c r="F182" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="G182" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="H182" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="I182" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="K182" s="1" t="s">
-        <v>408</v>
       </c>
     </row>
     <row r="183" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A183" s="1" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="B183" s="1" t="s">
         <v>13</v>
@@ -8111,7 +8111,7 @@
         <v>14</v>
       </c>
       <c r="D183" s="1" t="n">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="E183" s="1" t="n">
         <v>95</v>
@@ -8129,604 +8129,601 @@
         <v>0</v>
       </c>
       <c r="K183" s="1" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
     </row>
     <row r="184" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A184" s="1" t="s">
+        <v>410</v>
+      </c>
+      <c r="B184" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C184" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="D184" s="1" t="n">
+        <v>50</v>
+      </c>
+      <c r="E184" s="1" t="n">
+        <v>95</v>
+      </c>
+      <c r="F184" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="G184" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="H184" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="I184" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="K184" s="1" t="s">
         <v>411</v>
-      </c>
-      <c r="B184" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="C184" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="D184" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="E184" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="F184" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="G184" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="H184" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="I184" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="J184" s="4" t="n">
-        <v>38168</v>
-      </c>
-      <c r="K184" s="1" t="s">
-        <v>412</v>
       </c>
     </row>
     <row r="185" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A185" s="1" t="s">
+        <v>412</v>
+      </c>
+      <c r="B185" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C185" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D185" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="E185" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="F185" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="G185" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="H185" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="I185" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="J185" s="4" t="n">
+        <v>38168</v>
+      </c>
+      <c r="K185" s="1" t="s">
         <v>413</v>
-      </c>
-      <c r="B185" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="C185" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="D185" s="1" t="n">
-        <v>60</v>
-      </c>
-      <c r="E185" s="1" t="n">
-        <v>95</v>
-      </c>
-      <c r="F185" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="G185" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="H185" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="I185" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="K185" s="1" t="s">
-        <v>414</v>
       </c>
     </row>
     <row r="186" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A186" s="1" t="s">
+        <v>414</v>
+      </c>
+      <c r="B186" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C186" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="D186" s="1" t="n">
+        <v>60</v>
+      </c>
+      <c r="E186" s="1" t="n">
+        <v>95</v>
+      </c>
+      <c r="F186" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="G186" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="H186" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="I186" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="K186" s="1" t="s">
         <v>415</v>
-      </c>
-      <c r="B186" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="C186" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="D186" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="E186" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="F186" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="G186" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="H186" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="I186" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="J186" s="4" t="n">
-        <v>25723</v>
-      </c>
-      <c r="K186" s="1" t="s">
-        <v>416</v>
       </c>
     </row>
     <row r="187" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A187" s="1" t="s">
+        <v>416</v>
+      </c>
+      <c r="B187" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C187" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D187" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="E187" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="F187" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="G187" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="H187" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="I187" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="J187" s="4" t="n">
+        <v>25723</v>
+      </c>
+      <c r="K187" s="1" t="s">
         <v>417</v>
-      </c>
-      <c r="B187" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="C187" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="D187" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="E187" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="F187" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="G187" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="H187" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="I187" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="J187" s="4" t="n">
-        <v>36721</v>
-      </c>
-      <c r="K187" s="1" t="s">
-        <v>418</v>
       </c>
     </row>
     <row r="188" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A188" s="1" t="s">
+        <v>418</v>
+      </c>
+      <c r="B188" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C188" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D188" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="E188" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="F188" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="G188" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="H188" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="I188" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="J188" s="4" t="n">
+        <v>36721</v>
+      </c>
+      <c r="K188" s="1" t="s">
         <v>419</v>
-      </c>
-      <c r="B188" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="C188" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="D188" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="E188" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="F188" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="G188" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="H188" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="I188" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="J188" s="4" t="n">
-        <v>43189</v>
-      </c>
-      <c r="K188" s="1" t="s">
-        <v>420</v>
       </c>
     </row>
     <row r="189" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A189" s="1" t="s">
+        <v>420</v>
+      </c>
+      <c r="B189" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C189" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D189" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="E189" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="F189" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="G189" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="H189" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="I189" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="J189" s="4" t="n">
+        <v>43189</v>
+      </c>
+      <c r="K189" s="1" t="s">
         <v>421</v>
-      </c>
-      <c r="B189" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="C189" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="D189" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="E189" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="F189" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="G189" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="H189" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="I189" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="J189" s="4" t="n">
-        <v>31319</v>
-      </c>
-      <c r="K189" s="1" t="s">
-        <v>422</v>
       </c>
     </row>
     <row r="190" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A190" s="1" t="s">
+        <v>422</v>
+      </c>
+      <c r="B190" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C190" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D190" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="E190" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="F190" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="G190" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="H190" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="I190" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="J190" s="4" t="n">
+        <v>31319</v>
+      </c>
+      <c r="K190" s="1" t="s">
         <v>423</v>
-      </c>
-      <c r="B190" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="C190" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="D190" s="1" t="n">
-        <v>60</v>
-      </c>
-      <c r="E190" s="1" t="n">
-        <v>95</v>
-      </c>
-      <c r="F190" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="G190" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="H190" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="I190" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="K190" s="1" t="s">
-        <v>424</v>
       </c>
     </row>
     <row r="191" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A191" s="1" t="s">
+        <v>424</v>
+      </c>
+      <c r="B191" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C191" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="D191" s="1" t="n">
+        <v>60</v>
+      </c>
+      <c r="E191" s="1" t="n">
+        <v>95</v>
+      </c>
+      <c r="F191" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="G191" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="H191" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="I191" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="K191" s="1" t="s">
         <v>425</v>
-      </c>
-      <c r="B191" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="C191" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="D191" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="E191" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="F191" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="G191" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="H191" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="I191" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="J191" s="4" t="n">
-        <v>29067</v>
-      </c>
-      <c r="K191" s="1" t="s">
-        <v>426</v>
       </c>
     </row>
     <row r="192" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A192" s="1" t="s">
+        <v>426</v>
+      </c>
+      <c r="B192" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C192" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D192" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="E192" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="F192" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="G192" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="H192" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="I192" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="J192" s="4" t="n">
+        <v>29067</v>
+      </c>
+      <c r="K192" s="1" t="s">
         <v>427</v>
-      </c>
-      <c r="B192" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="C192" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="D192" s="1" t="n">
-        <v>60</v>
-      </c>
-      <c r="E192" s="1" t="n">
-        <v>95</v>
-      </c>
-      <c r="F192" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="G192" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="H192" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="I192" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="K192" s="1" t="s">
-        <v>428</v>
       </c>
     </row>
     <row r="193" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A193" s="1" t="s">
+        <v>428</v>
+      </c>
+      <c r="B193" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C193" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="D193" s="1" t="n">
+        <v>60</v>
+      </c>
+      <c r="E193" s="1" t="n">
+        <v>95</v>
+      </c>
+      <c r="F193" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="G193" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="H193" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="I193" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="K193" s="1" t="s">
         <v>429</v>
-      </c>
-      <c r="B193" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="C193" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="D193" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="E193" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="F193" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="G193" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="H193" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="I193" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="J193" s="4" t="n">
-        <v>37977</v>
-      </c>
-      <c r="K193" s="1" t="s">
-        <v>430</v>
       </c>
     </row>
     <row r="194" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A194" s="1" t="s">
+        <v>430</v>
+      </c>
+      <c r="B194" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C194" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D194" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="E194" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="F194" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="G194" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="H194" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="I194" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="J194" s="4" t="n">
+        <v>37977</v>
+      </c>
+      <c r="K194" s="1" t="s">
         <v>431</v>
-      </c>
-      <c r="B194" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="C194" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="D194" s="1" t="n">
-        <v>50</v>
-      </c>
-      <c r="E194" s="1" t="n">
-        <v>95</v>
-      </c>
-      <c r="F194" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="G194" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="H194" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="I194" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="K194" s="1" t="s">
-        <v>432</v>
       </c>
     </row>
     <row r="195" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A195" s="1" t="s">
+        <v>432</v>
+      </c>
+      <c r="B195" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C195" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="D195" s="1" t="n">
+        <v>50</v>
+      </c>
+      <c r="E195" s="1" t="n">
+        <v>95</v>
+      </c>
+      <c r="F195" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="G195" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="H195" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="I195" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="K195" s="1" t="s">
         <v>433</v>
-      </c>
-      <c r="B195" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="C195" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="D195" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="E195" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="F195" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="G195" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="H195" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="I195" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="J195" s="4" t="n">
-        <v>23766</v>
-      </c>
-      <c r="K195" s="1" t="s">
-        <v>434</v>
       </c>
     </row>
     <row r="196" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A196" s="1" t="s">
+        <v>434</v>
+      </c>
+      <c r="B196" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C196" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D196" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="E196" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="F196" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="G196" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="H196" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="I196" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="J196" s="4" t="n">
+        <v>23766</v>
+      </c>
+      <c r="K196" s="1" t="s">
         <v>435</v>
-      </c>
-      <c r="B196" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="C196" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="D196" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="E196" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="F196" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="G196" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="H196" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="I196" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="J196" s="4" t="n">
-        <v>41196</v>
-      </c>
-      <c r="K196" s="1" t="s">
-        <v>436</v>
       </c>
     </row>
     <row r="197" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A197" s="1" t="s">
+        <v>436</v>
+      </c>
+      <c r="B197" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C197" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D197" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="E197" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="F197" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="G197" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="H197" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="I197" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="J197" s="4" t="n">
+        <v>41196</v>
+      </c>
+      <c r="K197" s="1" t="s">
         <v>437</v>
-      </c>
-      <c r="B197" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="C197" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="D197" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="E197" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="F197" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="G197" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="H197" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="I197" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="J197" s="4" t="n">
-        <v>41014</v>
-      </c>
-      <c r="K197" s="1" t="s">
-        <v>438</v>
       </c>
     </row>
     <row r="198" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A198" s="1" t="s">
+        <v>438</v>
+      </c>
+      <c r="B198" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C198" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D198" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="E198" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="F198" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="G198" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="H198" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="I198" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="J198" s="4" t="n">
+        <v>41014</v>
+      </c>
+      <c r="K198" s="1" t="s">
         <v>439</v>
-      </c>
-      <c r="B198" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="C198" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="D198" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="E198" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="F198" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="G198" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="H198" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="I198" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="J198" s="4" t="n">
-        <v>29432</v>
-      </c>
-      <c r="K198" s="1" t="s">
-        <v>440</v>
       </c>
     </row>
     <row r="199" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A199" s="1" t="s">
+        <v>440</v>
+      </c>
+      <c r="B199" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C199" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D199" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="E199" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="F199" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="G199" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="H199" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="I199" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="J199" s="4" t="n">
+        <v>29432</v>
+      </c>
+      <c r="K199" s="1" t="s">
         <v>441</v>
-      </c>
-      <c r="B199" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="C199" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="D199" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="E199" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="F199" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="G199" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="H199" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="I199" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="J199" s="4" t="n">
-        <v>36235</v>
-      </c>
-      <c r="K199" s="1" t="s">
-        <v>442</v>
       </c>
     </row>
     <row r="200" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A200" s="1" t="s">
+        <v>442</v>
+      </c>
+      <c r="B200" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C200" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D200" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="E200" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="F200" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="G200" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="H200" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="I200" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="J200" s="4" t="n">
+        <v>36235</v>
+      </c>
+      <c r="K200" s="1" t="s">
         <v>443</v>
-      </c>
-      <c r="B200" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="C200" s="1" t="s">
-        <v>444</v>
-      </c>
-      <c r="D200" s="1" t="n">
-        <v>60</v>
-      </c>
-      <c r="E200" s="1" t="n">
-        <v>95</v>
-      </c>
-      <c r="F200" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="G200" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="H200" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="I200" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="J200" s="4" t="n">
-        <v>46276</v>
-      </c>
-      <c r="K200" s="1" t="s">
-        <v>445</v>
       </c>
     </row>
     <row r="201" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A201" s="1" t="s">
-        <v>446</v>
+        <v>444</v>
       </c>
       <c r="B201" s="1" t="s">
         <v>13</v>
       </c>
       <c r="C201" s="1" t="s">
-        <v>14</v>
+        <v>445</v>
       </c>
       <c r="D201" s="1" t="n">
-        <v>80</v>
+        <v>60</v>
       </c>
       <c r="E201" s="1" t="n">
         <v>95</v>
@@ -8743,13 +8740,16 @@
       <c r="I201" s="1" t="n">
         <v>0</v>
       </c>
+      <c r="J201" s="4" t="n">
+        <v>46276</v>
+      </c>
       <c r="K201" s="1" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
     </row>
     <row r="202" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A202" s="1" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="B202" s="1" t="s">
         <v>13</v>
@@ -8758,7 +8758,7 @@
         <v>14</v>
       </c>
       <c r="D202" s="1" t="n">
-        <v>60</v>
+        <v>80</v>
       </c>
       <c r="E202" s="1" t="n">
         <v>95</v>
@@ -8776,12 +8776,12 @@
         <v>0</v>
       </c>
       <c r="K202" s="1" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
     </row>
     <row r="203" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A203" s="1" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="B203" s="1" t="s">
         <v>13</v>
@@ -8808,10 +8808,41 @@
         <v>0</v>
       </c>
       <c r="K203" s="1" t="s">
+        <v>450</v>
+      </c>
+    </row>
+    <row r="204" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A204" s="1" t="s">
         <v>451</v>
       </c>
-    </row>
-    <row r="1048576" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+      <c r="B204" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C204" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="D204" s="1" t="n">
+        <v>60</v>
+      </c>
+      <c r="E204" s="1" t="n">
+        <v>95</v>
+      </c>
+      <c r="F204" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="G204" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="H204" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="I204" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="K204" s="1" t="s">
+        <v>452</v>
+      </c>
+    </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
